--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Кореньков- механик, водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Кореньков- механик, водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92576445794</v>
+        <v>46157.93121606708</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Кореньков- механик, водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Кореньков- механик, водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93121606708</v>
+        <v>46157.93187279153</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Кореньков- механик, водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Кореньков- механик, водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93187279153</v>
+        <v>46157.93408057994</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Кореньков- механик, водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Кореньков- механик, водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93408057994</v>
+        <v>46157.93725842111</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Кореньков- механик, водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Кореньков- механик, водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93725842111</v>
+        <v>46158.28223351399</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Кореньков- механик, водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Кореньков- механик, водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28223351399</v>
+        <v>46158.29714121639</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Кореньков- механик, водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Кореньков- механик, водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29714121639</v>
+        <v>46158.29823634039</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Кореньков- механик, водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Кореньков- механик, водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29823634039</v>
+        <v>46158.33394415771</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Кореньков- механик, водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Кореньков- механик, водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33394415771</v>
+        <v>46158.36864170552</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Кореньков- механик, водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Кореньков- механик, водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36864170552</v>
+        <v>46158.37295144777</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
